--- a/Week_1/HTTP 5310 – Capstone_Timeline_Ripal Patel.xlsx
+++ b/Week_1/HTTP 5310 – Capstone_Timeline_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Week_1</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Medium</t>
   </si>
   <si>
+    <t>Basic structure created</t>
+  </si>
+  <si>
     <t>Completed</t>
   </si>
   <si>
@@ -49,10 +52,28 @@
     <t>Easy</t>
   </si>
   <si>
+    <t>Add readme file &amp; GitHub Repo ready to use</t>
+  </si>
+  <si>
     <t>Create initial wireframes and feature list</t>
   </si>
   <si>
+    <t>Figma setup waiting for wireframe approval</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
     <t>Analyze healthcare websites to identify core features and UI patterns</t>
+  </si>
+  <si>
+    <t>Working on core features</t>
+  </si>
+  <si>
+    <t>Complete Requirements Document</t>
+  </si>
+  <si>
+    <t>Finilize Documents pending approval form instructor.</t>
   </si>
 </sst>
 </file>
@@ -350,10 +371,10 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.25"/>
+    <col customWidth="1" min="1" max="1" width="9.0"/>
     <col customWidth="1" min="2" max="2" width="66.0"/>
     <col customWidth="1" min="3" max="3" width="16.75"/>
-    <col customWidth="1" min="4" max="4" width="12.13"/>
+    <col customWidth="1" min="4" max="4" width="51.0"/>
     <col customWidth="1" min="5" max="5" width="10.0"/>
     <col customWidth="1" min="6" max="6" width="11.38"/>
   </cols>
@@ -408,10 +429,12 @@
       <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="E2" s="4"/>
       <c r="F2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="2"/>
@@ -437,15 +460,17 @@
     <row r="3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="2"/>
@@ -471,14 +496,18 @@
     <row r="4">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -503,15 +532,17 @@
     <row r="5">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="2"/>
@@ -535,13 +566,21 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>

--- a/Week_1/HTTP 5310 – Capstone_Timeline_Ripal Patel.xlsx
+++ b/Week_1/HTTP 5310 – Capstone_Timeline_Ripal Patel.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humber\Semester 3\Capstone Project\HealthCare Plus\Week_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humber\Semester 3\Capstone Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="67">
   <si>
     <t>Difficulty level</t>
   </si>
@@ -63,6 +63,12 @@
     <t>Complete Requirements Document</t>
   </si>
   <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
     <t>Week</t>
   </si>
   <si>
@@ -85,6 +91,135 @@
   </si>
   <si>
     <t>Draft requirements document prepared for instructor review</t>
+  </si>
+  <si>
+    <t>Week 2</t>
+  </si>
+  <si>
+    <t>Finalize wireframes and feature list</t>
+  </si>
+  <si>
+    <t>Wireframes updated based on feedback</t>
+  </si>
+  <si>
+    <t>Create project timeline and milestones</t>
+  </si>
+  <si>
+    <t>Complete Technical Barriers Assessment</t>
+  </si>
+  <si>
+    <t>Identified technical and content risks</t>
+  </si>
+  <si>
+    <t>Define UX goals and accessibility considerations</t>
+  </si>
+  <si>
+    <t>Accessibility and usability goals documented</t>
+  </si>
+  <si>
+    <t>Week 3</t>
+  </si>
+  <si>
+    <t>Set up front-end layout structure</t>
+  </si>
+  <si>
+    <t>Base layout and navigation implemented</t>
+  </si>
+  <si>
+    <t>Develop core pages</t>
+  </si>
+  <si>
+    <t>Home, doctor listing, and profile pages</t>
+  </si>
+  <si>
+    <t>Instructor check-in meeting</t>
+  </si>
+  <si>
+    <t>Progress discussion and feedback</t>
+  </si>
+  <si>
+    <t>Week 4</t>
+  </si>
+  <si>
+    <t>Conduct Figma user testing</t>
+  </si>
+  <si>
+    <t>Usability testing on prototype</t>
+  </si>
+  <si>
+    <t>Refine UI based on testing feedback</t>
+  </si>
+  <si>
+    <t>UI improvements and fixes applied</t>
+  </si>
+  <si>
+    <t>UI and UX review</t>
+  </si>
+  <si>
+    <t>Week 5</t>
+  </si>
+  <si>
+    <t>Implement core functionality</t>
+  </si>
+  <si>
+    <t>Appointment booking and user flows</t>
+  </si>
+  <si>
+    <t>Project proof-of-life</t>
+  </si>
+  <si>
+    <t>Demonstrate working application features</t>
+  </si>
+  <si>
+    <t>Functionality review</t>
+  </si>
+  <si>
+    <t>Week 6</t>
+  </si>
+  <si>
+    <t>End-to-end testing</t>
+  </si>
+  <si>
+    <t>Test full application workflow</t>
+  </si>
+  <si>
+    <t>Bug fixes and optimization</t>
+  </si>
+  <si>
+    <t>Resolve issues and improve performance</t>
+  </si>
+  <si>
+    <t>Final technical review</t>
+  </si>
+  <si>
+    <t>Week 7</t>
+  </si>
+  <si>
+    <t>Final project submission</t>
+  </si>
+  <si>
+    <t>Submit completed capstone project</t>
+  </si>
+  <si>
+    <t>Project presentation</t>
+  </si>
+  <si>
+    <t>Final demo and explanation</t>
+  </si>
+  <si>
+    <t>Submit project timesheet</t>
+  </si>
+  <si>
+    <t>Log and submit project hours</t>
+  </si>
+  <si>
+    <t>Launch portfolio with capstone project</t>
+  </si>
+  <si>
+    <t>Capstone added to personal portfolio</t>
+  </si>
+  <si>
+    <t>Timeline mathces course critical path</t>
   </si>
 </sst>
 </file>
@@ -112,7 +247,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -127,7 +262,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC9C9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFEDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFFECE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3FCFD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2CDFC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D2FE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -165,12 +336,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -408,7 +585,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G807"/>
+  <dimension ref="A1:G975"/>
   <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -421,123 +598,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+    <row r="2" spans="1:7" s="12" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
+      <c r="D4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3" t="s">
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
+      <c r="D7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A8" s="2"/>
@@ -548,46 +725,418 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="12.5" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A22" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A26" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="9"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:7" ht="12.5" x14ac:dyDescent="0.25"/>
     <row r="49" ht="12.5" x14ac:dyDescent="0.25"/>
     <row r="50" ht="12.5" x14ac:dyDescent="0.25"/>
     <row r="51" ht="12.5" x14ac:dyDescent="0.25"/>
@@ -1347,6 +1896,174 @@
     <row r="805" ht="12.5" x14ac:dyDescent="0.25"/>
     <row r="806" ht="12.5" x14ac:dyDescent="0.25"/>
     <row r="807" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="12.5" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
